--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,6 +1972,344 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118855697</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kärr+granskog+kulle, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572190</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7078120</v>
+      </c>
+      <c r="S14" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>"SCA hänsyn" vid knärotlokalen</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Erixon, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118855737</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96801</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kärr+granskog+kulle, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572190</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7078120</v>
+      </c>
+      <c r="S15" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anders Erixon, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118855750</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96807</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kärr+granskog+kulle, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572190</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7078120</v>
+      </c>
+      <c r="S16" t="n">
+        <v>100</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Erixon</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Erixon, Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SBF Florainventering i Ångermanland 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118263410</v>
+        <v>118263403</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572182</v>
+        <v>572181</v>
       </c>
       <c r="R3" t="n">
-        <v>7078128</v>
+        <v>7078141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118263408</v>
+        <v>118263398</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,25 +924,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572197</v>
+        <v>572190</v>
       </c>
       <c r="R4" t="n">
-        <v>7078254</v>
+        <v>7078253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118263404</v>
+        <v>118263408</v>
       </c>
       <c r="B5" t="n">
-        <v>96807</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572177</v>
+        <v>572197</v>
       </c>
       <c r="R5" t="n">
-        <v>7078195</v>
+        <v>7078254</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118263411</v>
+        <v>118263404</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>96807</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,25 +1128,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572182</v>
+        <v>572177</v>
       </c>
       <c r="R6" t="n">
-        <v>7078196</v>
+        <v>7078195</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118263398</v>
+        <v>118263399</v>
       </c>
       <c r="B7" t="n">
-        <v>90504</v>
+        <v>57443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,34 +1234,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Barrnaturskog sydväst om Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572190</v>
+        <v>572231</v>
       </c>
       <c r="R7" t="n">
-        <v>7078253</v>
+        <v>7078288</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,14 +1321,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Anders Erixon</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118263406</v>
+        <v>118263410</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1360,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572233</v>
+        <v>572182</v>
       </c>
       <c r="R8" t="n">
-        <v>7078288</v>
+        <v>7078128</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,10 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118263403</v>
+        <v>118263409</v>
       </c>
       <c r="B9" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,25 +1442,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1470,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572181</v>
+        <v>572167</v>
       </c>
       <c r="R9" t="n">
-        <v>7078141</v>
+        <v>7078178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,10 +1532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118263399</v>
+        <v>118263411</v>
       </c>
       <c r="B10" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,46 +1544,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Barrnaturskog sydväst om Källmyrtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572231</v>
+        <v>572182</v>
       </c>
       <c r="R10" t="n">
-        <v>7078288</v>
+        <v>7078196</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1627,14 +1627,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Anders Erixon</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118263409</v>
+        <v>118263406</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572167</v>
+        <v>572233</v>
       </c>
       <c r="R11" t="n">
-        <v>7078178</v>
+        <v>7078288</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118409881</v>
+        <v>118409905</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1781,21 +1781,21 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>25m N om tjärn, Ång</t>
+          <t>20m NO om tjärn, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572206</v>
+        <v>572220</v>
       </c>
       <c r="R12" t="n">
-        <v>7078271</v>
+        <v>7078269</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118409905</v>
+        <v>118409881</v>
       </c>
       <c r="B13" t="n">
         <v>97846</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,21 +1900,21 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20m NO om tjärn, Ång</t>
+          <t>25m N om tjärn, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572220</v>
+        <v>572206</v>
       </c>
       <c r="R13" t="n">
-        <v>7078269</v>
+        <v>7078271</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118855737</v>
+        <v>118855750</v>
       </c>
       <c r="B15" t="n">
-        <v>96801</v>
+        <v>96807</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118855750</v>
+        <v>118855737</v>
       </c>
       <c r="B16" t="n">
-        <v>96807</v>
+        <v>96801</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -1736,10 +1736,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118409905</v>
+        <v>118409881</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1781,21 +1781,21 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>20m NO om tjärn, Ång</t>
+          <t>25m N om tjärn, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572220</v>
+        <v>572206</v>
       </c>
       <c r="R12" t="n">
-        <v>7078269</v>
+        <v>7078271</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118409881</v>
+        <v>118409905</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,21 +1900,21 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>25m N om tjärn, Ång</t>
+          <t>20m NO om tjärn, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572206</v>
+        <v>572220</v>
       </c>
       <c r="R13" t="n">
-        <v>7078271</v>
+        <v>7078269</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,7 +1977,7 @@
         <v>118855697</v>
       </c>
       <c r="B14" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>118855750</v>
       </c>
       <c r="B15" t="n">
-        <v>96807</v>
+        <v>96814</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>118855737</v>
       </c>
       <c r="B16" t="n">
-        <v>96801</v>
+        <v>96808</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -1736,7 +1736,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118409881</v>
+        <v>118409905</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1781,21 +1781,21 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>25m N om tjärn, Ång</t>
+          <t>20m NO om tjärn, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572206</v>
+        <v>572220</v>
       </c>
       <c r="R12" t="n">
-        <v>7078271</v>
+        <v>7078269</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118409905</v>
+        <v>118409881</v>
       </c>
       <c r="B13" t="n">
         <v>97853</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1900,21 +1900,21 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20m NO om tjärn, Ång</t>
+          <t>25m N om tjärn, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572220</v>
+        <v>572206</v>
       </c>
       <c r="R13" t="n">
-        <v>7078269</v>
+        <v>7078271</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118855750</v>
+        <v>118855737</v>
       </c>
       <c r="B15" t="n">
-        <v>96814</v>
+        <v>96808</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2106,16 +2106,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118855737</v>
+        <v>118855750</v>
       </c>
       <c r="B16" t="n">
-        <v>96808</v>
+        <v>96814</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2310,6 +2310,1046 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127838658</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572220</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7078329</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127840428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>572204</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7078038</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127838705</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>572197</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7078292</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127840339</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>572223</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7078016</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127840457</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>572193</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7078038</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127839277</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>572189</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7078246</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127839160</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>572192</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7078274</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127840356</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>572218</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7078017</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127838783</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91358</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>572191</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7078278</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2315,7 +2315,7 @@
         <v>127838658</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,42 +2429,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127840428</v>
+        <v>127838705</v>
       </c>
       <c r="B18" t="n">
-        <v>98456</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2473,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572204</v>
+        <v>572197</v>
       </c>
       <c r="R18" t="n">
-        <v>7078038</v>
+        <v>7078292</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2504,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2518,7 +2514,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,38 +2546,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127838705</v>
+        <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>98459</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2585,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572197</v>
+        <v>572204</v>
       </c>
       <c r="R19" t="n">
-        <v>7078292</v>
+        <v>7078038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2620,7 +2625,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2635,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>127840457</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127839277</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>91361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,39 +3139,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R24" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,12 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B25" t="n">
-        <v>91358</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,34 +3246,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R25" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3315,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,7 +3320,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2315,7 +2315,7 @@
         <v>127838658</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>127838705</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>127840457</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127839277</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>127838783</v>
       </c>
       <c r="B24" t="n">
-        <v>91361</v>
+        <v>91369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>127840356</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2549,7 +2549,7 @@
         <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B24" t="n">
-        <v>91369</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,34 +3139,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R24" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,7 +3203,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,7 +3213,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3245,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>91370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,39 +3256,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R25" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,12 +3325,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2549,7 +2549,7 @@
         <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>127838783</v>
       </c>
       <c r="B25" t="n">
-        <v>91370</v>
+        <v>91371</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2549,7 +2549,7 @@
         <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,39 +3139,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R24" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,12 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B25" t="n">
-        <v>91371</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,34 +3246,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R25" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3315,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,7 +3320,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B24" t="n">
-        <v>91372</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,34 +3139,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R24" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,7 +3203,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,7 +3213,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3245,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>91372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,39 +3256,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R25" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,12 +3325,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>91372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,39 +3139,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R24" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,12 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B25" t="n">
-        <v>91372</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,34 +3246,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R25" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3315,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,7 +3320,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2315,7 +2315,7 @@
         <v>127838658</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>127838705</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>127840457</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127839277</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B24" t="n">
-        <v>91372</v>
+        <v>57673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,34 +3139,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R24" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,7 +3203,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3208,7 +3213,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,10 +3245,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>91380</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3246,39 +3256,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R25" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3310,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,12 +3325,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2315,7 +2315,7 @@
         <v>127838658</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,38 +2429,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127838705</v>
+        <v>127840428</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2469,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572197</v>
+        <v>572204</v>
       </c>
       <c r="R18" t="n">
-        <v>7078292</v>
+        <v>7078038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,7 +2508,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2514,12 +2518,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,42 +2545,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127840428</v>
+        <v>127838705</v>
       </c>
       <c r="B19" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2590,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572204</v>
+        <v>572197</v>
       </c>
       <c r="R19" t="n">
-        <v>7078038</v>
+        <v>7078292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2635,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2665,7 +2665,7 @@
         <v>127840339</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>127840457</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>127839277</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>127839160</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127840356</v>
+        <v>127838783</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>91472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3139,39 +3139,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>572218</v>
+        <v>572191</v>
       </c>
       <c r="R24" t="n">
-        <v>7078017</v>
+        <v>7078278</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3203,7 +3198,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,12 +3208,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3245,10 +3235,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127838783</v>
+        <v>127840356</v>
       </c>
       <c r="B25" t="n">
-        <v>91380</v>
+        <v>57685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3256,34 +3246,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>572191</v>
+        <v>572218</v>
       </c>
       <c r="R25" t="n">
-        <v>7078278</v>
+        <v>7078017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3315,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,7 +3320,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2429,42 +2429,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127840428</v>
+        <v>127838705</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2473,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572204</v>
+        <v>572197</v>
       </c>
       <c r="R18" t="n">
-        <v>7078038</v>
+        <v>7078292</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2504,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2518,7 +2514,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,38 +2546,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127838705</v>
+        <v>127840428</v>
       </c>
       <c r="B19" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2585,10 +2590,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572197</v>
+        <v>572204</v>
       </c>
       <c r="R19" t="n">
-        <v>7078292</v>
+        <v>7078038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2620,7 +2625,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2635,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -2429,38 +2429,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127838705</v>
+        <v>127840428</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2469,10 +2473,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572197</v>
+        <v>572204</v>
       </c>
       <c r="R18" t="n">
-        <v>7078292</v>
+        <v>7078038</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,7 +2508,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2514,12 +2518,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,42 +2545,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127840428</v>
+        <v>127838705</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2590,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572204</v>
+        <v>572197</v>
       </c>
       <c r="R19" t="n">
-        <v>7078038</v>
+        <v>7078292</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2635,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,42 +3363,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R26" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,24 +3420,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3465,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R27" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,14 +3527,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,44 +3559,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128968877</v>
+        <v>128968881</v>
       </c>
       <c r="B28" t="n">
-        <v>79653</v>
+        <v>97522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572283</v>
+        <v>572238</v>
       </c>
       <c r="R28" t="n">
-        <v>7078294</v>
+        <v>7078279</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128968881</v>
+        <v>128968877</v>
       </c>
       <c r="B29" t="n">
-        <v>97522</v>
+        <v>79653</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572238</v>
+        <v>572283</v>
       </c>
       <c r="R29" t="n">
-        <v>7078279</v>
+        <v>7078294</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -5834,48 +5834,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B50" t="n">
-        <v>92811</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R50" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,19 +5902,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,22 +5919,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968880</v>
+        <v>128966090</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,37 +5942,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572367</v>
+        <v>572227</v>
       </c>
       <c r="R51" t="n">
-        <v>7078119</v>
+        <v>7078263</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,9 +6004,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,62 +6036,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>92811</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R52" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,7 +6118,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6123,12 +6128,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,65 +6143,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>92811</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R53" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6228,24 +6223,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6260,60 +6240,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>92811</v>
+        <v>79034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R54" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6340,9 +6320,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,22 +6347,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,34 +6370,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6439,7 +6434,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6449,7 +6444,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128968881</v>
+        <v>128968877</v>
       </c>
       <c r="B28" t="n">
-        <v>97522</v>
+        <v>79653</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572238</v>
+        <v>572283</v>
       </c>
       <c r="R28" t="n">
-        <v>7078279</v>
+        <v>7078294</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128968877</v>
+        <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>79653</v>
+        <v>97527</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572283</v>
+        <v>572238</v>
       </c>
       <c r="R29" t="n">
-        <v>7078294</v>
+        <v>7078279</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,48 +4172,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B34" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R34" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,9 +4245,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,65 +4277,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>92816</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R35" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4342,24 +4357,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R38" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,11 +4671,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R39" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4773,6 +4768,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968889</v>
+        <v>128965337</v>
       </c>
       <c r="B42" t="n">
         <v>79034</v>
@@ -5054,17 +5054,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572173</v>
+        <v>572328</v>
       </c>
       <c r="R42" t="n">
-        <v>7078310</v>
+        <v>7078189</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,14 +5091,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5113,22 +5118,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128965337</v>
+        <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5141,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5160,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572328</v>
+        <v>572174</v>
       </c>
       <c r="R43" t="n">
-        <v>7078189</v>
+        <v>7078301</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,7 +5200,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5205,7 +5210,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5225,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964737</v>
+        <v>128968889</v>
       </c>
       <c r="B44" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,37 +5248,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572174</v>
+        <v>572173</v>
       </c>
       <c r="R44" t="n">
-        <v>7078301</v>
+        <v>7078310</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5300,19 +5305,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>98656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R48" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>79034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R49" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128968880</v>
+        <v>128966090</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5845,37 +5845,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572367</v>
+        <v>572227</v>
       </c>
       <c r="R50" t="n">
-        <v>7078119</v>
+        <v>7078263</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,9 +5907,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5919,62 +5939,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>92816</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R51" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6006,7 +6021,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6016,12 +6031,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6036,60 +6046,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B52" t="n">
-        <v>92811</v>
+        <v>91543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R52" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6116,19 +6126,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,12 +6143,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
         <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96140</v>
+        <v>96145</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,37 +3363,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R26" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3420,14 +3425,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3457,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,42 +3480,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R27" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3527,24 +3537,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,44 +3559,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128968877</v>
+        <v>128968881</v>
       </c>
       <c r="B28" t="n">
-        <v>79653</v>
+        <v>97530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572283</v>
+        <v>572238</v>
       </c>
       <c r="R28" t="n">
-        <v>7078294</v>
+        <v>7078279</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128968881</v>
+        <v>128968877</v>
       </c>
       <c r="B29" t="n">
-        <v>97527</v>
+        <v>79654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572238</v>
+        <v>572283</v>
       </c>
       <c r="R29" t="n">
-        <v>7078279</v>
+        <v>7078294</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>128968884</v>
       </c>
       <c r="B32" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>128968876</v>
       </c>
       <c r="B33" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>128968896</v>
       </c>
       <c r="B35" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B38" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R38" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,6 +4671,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4697,10 +4702,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4732,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R39" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4768,11 +4773,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128965337</v>
+        <v>128968889</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5054,17 +5054,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572328</v>
+        <v>572173</v>
       </c>
       <c r="R42" t="n">
-        <v>7078189</v>
+        <v>7078310</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,19 +5091,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5118,12 +5113,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5133,7 +5128,7 @@
         <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5237,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968889</v>
+        <v>128965337</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5268,17 +5263,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572173</v>
+        <v>572328</v>
       </c>
       <c r="R44" t="n">
-        <v>7078310</v>
+        <v>7078189</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5305,14 +5300,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128968878</v>
+        <v>128965015</v>
       </c>
       <c r="B46" t="n">
-        <v>91523</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5447,37 +5447,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572196</v>
+        <v>572270</v>
       </c>
       <c r="R46" t="n">
-        <v>7078225</v>
+        <v>7078288</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5504,9 +5504,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5521,22 +5531,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128965015</v>
+        <v>128968878</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>91526</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5544,37 +5554,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572270</v>
+        <v>572196</v>
       </c>
       <c r="R47" t="n">
-        <v>7078288</v>
+        <v>7078225</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5601,19 +5611,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,44 +5628,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B48" t="n">
-        <v>98656</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R48" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R49" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128966090</v>
+        <v>128968880</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>91546</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5845,42 +5845,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572227</v>
+        <v>572367</v>
       </c>
       <c r="R50" t="n">
-        <v>7078263</v>
+        <v>7078119</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5907,24 +5902,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,12 +5919,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5954,7 +5934,7 @@
         <v>128964698</v>
       </c>
       <c r="B51" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6058,10 +6038,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128968880</v>
+        <v>128966090</v>
       </c>
       <c r="B52" t="n">
-        <v>91543</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6069,37 +6049,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572367</v>
+        <v>572227</v>
       </c>
       <c r="R52" t="n">
-        <v>7078119</v>
+        <v>7078263</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6126,9 +6111,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,12 +6143,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
         <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96145</v>
+        <v>96148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,42 +3363,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R26" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,24 +3420,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3465,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R27" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,14 +3527,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,44 +3559,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128968881</v>
+        <v>128968877</v>
       </c>
       <c r="B28" t="n">
-        <v>97530</v>
+        <v>79654</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572238</v>
+        <v>572283</v>
       </c>
       <c r="R28" t="n">
-        <v>7078279</v>
+        <v>7078294</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128968877</v>
+        <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>97530</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572283</v>
+        <v>572238</v>
       </c>
       <c r="R29" t="n">
-        <v>7078294</v>
+        <v>7078279</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4172,53 +4172,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R34" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,24 +4240,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,60 +4257,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B35" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R35" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,9 +4342,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,37 +5034,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R42" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,14 +5091,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5113,22 +5118,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B43" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5141,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5160,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R43" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,7 +5200,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5205,7 +5210,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,60 +5225,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128965337</v>
+        <v>128968885</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572328</v>
+        <v>572164</v>
       </c>
       <c r="R44" t="n">
-        <v>7078189</v>
+        <v>7078161</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5300,19 +5305,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,44 +5322,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968885</v>
+        <v>128968889</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5374,10 +5369,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572164</v>
+        <v>572173</v>
       </c>
       <c r="R45" t="n">
-        <v>7078161</v>
+        <v>7078310</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5410,6 +5405,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5436,10 +5436,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128965015</v>
+        <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5447,37 +5447,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572270</v>
+        <v>572196</v>
       </c>
       <c r="R46" t="n">
-        <v>7078288</v>
+        <v>7078225</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5504,19 +5504,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5531,22 +5521,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128968878</v>
+        <v>128965015</v>
       </c>
       <c r="B47" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5554,37 +5544,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572196</v>
+        <v>572270</v>
       </c>
       <c r="R47" t="n">
-        <v>7078225</v>
+        <v>7078288</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5611,9 +5601,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,12 +5628,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5834,48 +5834,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128968880</v>
+        <v>128964698</v>
       </c>
       <c r="B50" t="n">
-        <v>91546</v>
+        <v>92819</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572367</v>
+        <v>572170</v>
       </c>
       <c r="R50" t="n">
-        <v>7078119</v>
+        <v>7078313</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,9 +5902,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5919,60 +5929,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>92819</v>
+        <v>91546</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R51" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5999,19 +6009,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,12 +6026,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128968877</v>
+        <v>128968881</v>
       </c>
       <c r="B28" t="n">
-        <v>79654</v>
+        <v>97530</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572283</v>
+        <v>572238</v>
       </c>
       <c r="R28" t="n">
-        <v>7078294</v>
+        <v>7078279</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128968881</v>
+        <v>128968877</v>
       </c>
       <c r="B29" t="n">
-        <v>97530</v>
+        <v>79654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572238</v>
+        <v>572283</v>
       </c>
       <c r="R29" t="n">
-        <v>7078279</v>
+        <v>7078294</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -5834,48 +5834,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B50" t="n">
-        <v>92819</v>
+        <v>91546</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R50" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,19 +5902,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,60 +5919,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968880</v>
+        <v>128964698</v>
       </c>
       <c r="B51" t="n">
-        <v>91546</v>
+        <v>92819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572367</v>
+        <v>572170</v>
       </c>
       <c r="R51" t="n">
-        <v>7078119</v>
+        <v>7078313</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,9 +5999,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,12 +6026,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,37 +3363,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R26" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3420,14 +3425,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3457,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B27" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,42 +3480,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R27" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3527,24 +3537,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R38" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,11 +4671,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R39" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4773,6 +4768,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5130,7 +5130,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128965337</v>
+        <v>128968889</v>
       </c>
       <c r="B43" t="n">
         <v>79035</v>
@@ -5161,17 +5161,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572328</v>
+        <v>572173</v>
       </c>
       <c r="R43" t="n">
-        <v>7078189</v>
+        <v>7078310</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,19 +5198,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5225,60 +5220,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968885</v>
+        <v>128965337</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572164</v>
+        <v>572328</v>
       </c>
       <c r="R44" t="n">
-        <v>7078161</v>
+        <v>7078189</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5305,9 +5300,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5322,44 +5327,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968889</v>
+        <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5369,10 +5374,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572173</v>
+        <v>572164</v>
       </c>
       <c r="R45" t="n">
-        <v>7078310</v>
+        <v>7078161</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5405,11 +5410,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5834,48 +5834,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128968880</v>
+        <v>128964698</v>
       </c>
       <c r="B50" t="n">
-        <v>91546</v>
+        <v>92819</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572367</v>
+        <v>572170</v>
       </c>
       <c r="R50" t="n">
-        <v>7078119</v>
+        <v>7078313</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,9 +5902,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5919,60 +5929,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>92819</v>
+        <v>91546</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R51" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5999,19 +6009,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,12 +6026,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6155,48 +6155,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968894</v>
+        <v>128965429</v>
       </c>
       <c r="B53" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572170</v>
+        <v>572345</v>
       </c>
       <c r="R53" t="n">
-        <v>7078122</v>
+        <v>7078154</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,9 +6228,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,60 +6260,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R54" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6320,19 +6340,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6347,22 +6357,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128965429</v>
+        <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,39 +6380,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572345</v>
+        <v>572171</v>
       </c>
       <c r="R55" t="n">
-        <v>7078154</v>
+        <v>7078312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,7 +6439,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6444,12 +6449,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3355,7 +3355,7 @@
         <v>128965870</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>128968887</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3571,32 +3571,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128968881</v>
+        <v>128968877</v>
       </c>
       <c r="B28" t="n">
-        <v>97530</v>
+        <v>79658</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>572238</v>
+        <v>572283</v>
       </c>
       <c r="R28" t="n">
-        <v>7078279</v>
+        <v>7078294</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128968877</v>
+        <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>79654</v>
+        <v>97540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>572283</v>
+        <v>572238</v>
       </c>
       <c r="R29" t="n">
-        <v>7078294</v>
+        <v>7078279</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>128968884</v>
       </c>
       <c r="B32" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>128968876</v>
       </c>
       <c r="B33" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>128965271</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>128965587</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B42" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,21 +5034,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R42" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5118,22 +5118,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5141,37 +5141,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R43" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,14 +5198,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5225,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128965337</v>
+        <v>128968889</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5263,17 +5268,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572328</v>
+        <v>572173</v>
       </c>
       <c r="R44" t="n">
-        <v>7078189</v>
+        <v>7078310</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5300,19 +5305,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128968878</v>
+        <v>128965015</v>
       </c>
       <c r="B46" t="n">
-        <v>91526</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5447,37 +5447,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572196</v>
+        <v>572270</v>
       </c>
       <c r="R46" t="n">
-        <v>7078225</v>
+        <v>7078288</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5504,9 +5504,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5521,22 +5531,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128965015</v>
+        <v>128968878</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>91533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5544,37 +5554,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572270</v>
+        <v>572196</v>
       </c>
       <c r="R47" t="n">
-        <v>7078288</v>
+        <v>7078225</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5601,19 +5611,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,44 +5628,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R48" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R49" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,48 +5834,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B50" t="n">
-        <v>92819</v>
+        <v>91553</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R50" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,19 +5902,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,60 +5919,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968880</v>
+        <v>128964698</v>
       </c>
       <c r="B51" t="n">
-        <v>91546</v>
+        <v>92826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572367</v>
+        <v>572170</v>
       </c>
       <c r="R51" t="n">
-        <v>7078119</v>
+        <v>7078313</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,9 +5999,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,12 +6026,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6041,7 +6041,7 @@
         <v>128966090</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128965429</v>
+        <v>128964712</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,39 +6166,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572345</v>
+        <v>572171</v>
       </c>
       <c r="R53" t="n">
-        <v>7078154</v>
+        <v>7078312</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6230,7 +6225,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6240,12 +6235,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6272,48 +6262,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968894</v>
+        <v>128965429</v>
       </c>
       <c r="B54" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572170</v>
+        <v>572345</v>
       </c>
       <c r="R54" t="n">
-        <v>7078122</v>
+        <v>7078154</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6340,9 +6335,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,60 +6367,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>92826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6437,19 +6447,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6464,12 +6464,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96148</v>
+        <v>96158</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B48" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R48" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R49" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6155,10 +6155,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6166,34 +6166,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R53" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6225,7 +6230,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6235,7 +6240,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,53 +6272,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B54" t="n">
-        <v>57725</v>
+        <v>92826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R54" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6335,24 +6340,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6367,60 +6357,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R55" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6447,9 +6437,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6464,12 +6464,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,48 +4172,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B34" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R34" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,9 +4245,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,65 +4277,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>92833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R35" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4342,24 +4357,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128964737</v>
+        <v>128968889</v>
       </c>
       <c r="B43" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5141,37 +5141,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572174</v>
+        <v>572173</v>
       </c>
       <c r="R43" t="n">
-        <v>7078301</v>
+        <v>7078310</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,19 +5198,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5225,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>78796</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5248,37 +5243,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R44" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5305,14 +5300,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128965015</v>
+        <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5447,37 +5447,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>572270</v>
+        <v>572196</v>
       </c>
       <c r="R46" t="n">
-        <v>7078288</v>
+        <v>7078225</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5504,19 +5504,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5531,22 +5521,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128968878</v>
+        <v>128965015</v>
       </c>
       <c r="B47" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5554,37 +5544,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>572196</v>
+        <v>572270</v>
       </c>
       <c r="R47" t="n">
-        <v>7078225</v>
+        <v>7078288</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5611,9 +5601,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,12 +5628,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5740,7 +5740,7 @@
         <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128968880</v>
       </c>
       <c r="B50" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128964698</v>
       </c>
       <c r="B51" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6155,53 +6155,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>92833</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R53" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6228,24 +6223,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6260,60 +6240,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R54" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6340,9 +6320,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,22 +6347,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,34 +6370,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6439,7 +6434,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6449,7 +6444,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,42 +3363,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R26" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,24 +3420,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3465,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R27" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,14 +3527,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
         <v>128968877</v>
       </c>
       <c r="B28" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>128968884</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>128968876</v>
       </c>
       <c r="B33" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4172,53 +4172,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R34" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,24 +4240,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,60 +4257,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B35" t="n">
-        <v>92833</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R35" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,9 +4342,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>128965587</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128965337</v>
+        <v>128968889</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5054,17 +5054,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572328</v>
+        <v>572173</v>
       </c>
       <c r="R42" t="n">
-        <v>7078189</v>
+        <v>7078310</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,19 +5091,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5118,22 +5113,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>78798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5141,37 +5136,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R43" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,14 +5193,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B44" t="n">
-        <v>78796</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R44" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>128965015</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128968890</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128968880</v>
+        <v>128966090</v>
       </c>
       <c r="B50" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5845,37 +5845,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572367</v>
+        <v>572227</v>
       </c>
       <c r="R50" t="n">
-        <v>7078119</v>
+        <v>7078263</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5902,9 +5907,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5919,60 +5939,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>92833</v>
+        <v>91562</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R51" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5999,19 +6019,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,62 +6036,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R52" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,7 +6118,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6123,12 +6128,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,12 +6143,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6158,7 +6158,7 @@
         <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>128965429</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,37 +3363,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R26" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3420,14 +3425,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3457,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,42 +3480,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R27" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3527,24 +3537,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -5834,50 +5834,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R50" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5909,7 +5904,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5919,12 +5914,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,12 +5929,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6048,45 +6038,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128964698</v>
+        <v>128966090</v>
       </c>
       <c r="B52" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572170</v>
+        <v>572227</v>
       </c>
       <c r="R52" t="n">
-        <v>7078313</v>
+        <v>7078263</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6118,7 +6113,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6128,7 +6123,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,12 +6143,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6252,10 +6252,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,34 +6263,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R54" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6322,7 +6327,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6332,7 +6337,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6359,10 +6369,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128965429</v>
+        <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,39 +6380,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572345</v>
+        <v>572171</v>
       </c>
       <c r="R55" t="n">
-        <v>7078154</v>
+        <v>7078312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,7 +6439,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6444,12 +6449,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -5023,32 +5023,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968889</v>
+        <v>128968885</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572173</v>
+        <v>572164</v>
       </c>
       <c r="R42" t="n">
-        <v>7078310</v>
+        <v>7078161</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5094,11 +5094,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5125,10 +5120,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128964737</v>
+        <v>128968889</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,37 +5131,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572174</v>
+        <v>572173</v>
       </c>
       <c r="R43" t="n">
-        <v>7078301</v>
+        <v>7078310</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5193,19 +5188,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5210,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128965337</v>
+        <v>128964737</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5233,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5257,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572328</v>
+        <v>572174</v>
       </c>
       <c r="R44" t="n">
-        <v>7078189</v>
+        <v>7078301</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5292,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5312,7 +5302,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,60 +5317,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968885</v>
+        <v>128965337</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572164</v>
+        <v>572328</v>
       </c>
       <c r="R45" t="n">
-        <v>7078161</v>
+        <v>7078189</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5407,9 +5397,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5424,12 +5424,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6155,48 +6155,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B53" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R53" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,9 +6223,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,65 +6250,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R54" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6325,24 +6330,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,22 +6347,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,34 +6370,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6439,7 +6434,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6449,7 +6444,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,32 +5023,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968885</v>
+        <v>128968889</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572164</v>
+        <v>572173</v>
       </c>
       <c r="R42" t="n">
-        <v>7078161</v>
+        <v>7078310</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5094,6 +5094,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5120,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5131,37 +5136,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R43" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5188,14 +5193,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5210,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5233,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5257,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R44" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5292,7 +5302,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5302,7 +5312,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,60 +5327,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128965337</v>
+        <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572328</v>
+        <v>572164</v>
       </c>
       <c r="R45" t="n">
-        <v>7078189</v>
+        <v>7078161</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5397,19 +5407,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5424,12 +5424,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R48" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B49" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R49" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,45 +5834,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128964698</v>
+        <v>128966090</v>
       </c>
       <c r="B50" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572170</v>
+        <v>572227</v>
       </c>
       <c r="R50" t="n">
-        <v>7078313</v>
+        <v>7078263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,7 +5909,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5914,7 +5919,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,12 +5939,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5944,7 +5954,7 @@
         <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6038,50 +6048,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>92821</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R52" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6113,7 +6118,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6123,12 +6128,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,60 +6143,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>92821</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R53" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,19 +6223,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6250,60 +6240,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R54" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6330,9 +6320,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6347,12 +6347,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,42 +3363,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R26" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,24 +3420,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3465,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R27" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,14 +3527,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,48 +4172,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B34" t="n">
-        <v>92821</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R34" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,9 +4245,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,65 +4277,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R35" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4342,24 +4357,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B48" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R48" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R49" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5954,7 +5954,7 @@
         <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>128964698</v>
       </c>
       <c r="B52" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,48 +6155,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968894</v>
+        <v>128965429</v>
       </c>
       <c r="B53" t="n">
-        <v>92821</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572170</v>
+        <v>572345</v>
       </c>
       <c r="R53" t="n">
-        <v>7078122</v>
+        <v>7078154</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,9 +6228,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,60 +6260,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R54" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6320,19 +6340,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6347,22 +6357,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128965429</v>
+        <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,39 +6380,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572345</v>
+        <v>572171</v>
       </c>
       <c r="R55" t="n">
-        <v>7078154</v>
+        <v>7078312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,7 +6439,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6444,12 +6449,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,53 +4172,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R34" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,24 +4240,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,60 +4257,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B35" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R35" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,9 +4342,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968889</v>
+        <v>128965337</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -5054,17 +5054,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572173</v>
+        <v>572328</v>
       </c>
       <c r="R42" t="n">
-        <v>7078310</v>
+        <v>7078189</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,14 +5091,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5113,22 +5118,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128964737</v>
+        <v>128968889</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,37 +5141,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572174</v>
+        <v>572173</v>
       </c>
       <c r="R43" t="n">
-        <v>7078301</v>
+        <v>7078310</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5193,19 +5198,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128965337</v>
+        <v>128964737</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572328</v>
+        <v>572174</v>
       </c>
       <c r="R44" t="n">
-        <v>7078189</v>
+        <v>7078301</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R48" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B49" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R49" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,50 +5834,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R50" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5909,7 +5904,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5919,12 +5914,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,12 +5929,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6048,45 +6038,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128964698</v>
+        <v>128966090</v>
       </c>
       <c r="B52" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572170</v>
+        <v>572227</v>
       </c>
       <c r="R52" t="n">
-        <v>7078313</v>
+        <v>7078263</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6118,7 +6113,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6128,7 +6123,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,65 +6143,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>92822</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R53" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6228,24 +6223,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6260,60 +6240,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>92822</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R54" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6340,9 +6320,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,22 +6347,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6380,34 +6370,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6439,7 +6434,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6449,7 +6444,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,37 +3363,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R26" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3420,14 +3425,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3457,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,42 +3480,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R27" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3527,24 +3537,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
         <v>128968877</v>
       </c>
       <c r="B28" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>128968884</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>128968876</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B38" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R38" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,6 +4671,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4697,10 +4702,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4732,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R39" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4768,11 +4773,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>128965337</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5130,32 +5130,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968889</v>
+        <v>128968885</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572173</v>
+        <v>572164</v>
       </c>
       <c r="R43" t="n">
-        <v>7078310</v>
+        <v>7078161</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5201,11 +5201,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964737</v>
+        <v>128968889</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,37 +5238,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572174</v>
+        <v>572173</v>
       </c>
       <c r="R44" t="n">
-        <v>7078301</v>
+        <v>7078310</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5300,19 +5295,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:24</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,60 +5317,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968885</v>
+        <v>128964737</v>
       </c>
       <c r="B45" t="n">
-        <v>98706</v>
+        <v>78800</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572164</v>
+        <v>572174</v>
       </c>
       <c r="R45" t="n">
-        <v>7078161</v>
+        <v>7078301</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5407,9 +5397,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5424,12 +5424,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>128965015</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B48" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R48" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R49" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5837,7 +5837,7 @@
         <v>128964698</v>
       </c>
       <c r="B50" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968880</v>
+        <v>128966090</v>
       </c>
       <c r="B51" t="n">
-        <v>91561</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,37 +5952,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572367</v>
+        <v>572227</v>
       </c>
       <c r="R51" t="n">
-        <v>7078119</v>
+        <v>7078263</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,9 +6014,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,22 +6046,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128966090</v>
+        <v>128968880</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6049,42 +6069,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572227</v>
+        <v>572367</v>
       </c>
       <c r="R52" t="n">
-        <v>7078263</v>
+        <v>7078119</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6111,24 +6126,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,60 +6143,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968894</v>
+        <v>128965429</v>
       </c>
       <c r="B53" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572170</v>
+        <v>572345</v>
       </c>
       <c r="R53" t="n">
-        <v>7078122</v>
+        <v>7078154</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,9 +6228,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,60 +6260,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R54" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6320,19 +6340,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6347,22 +6357,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128965429</v>
+        <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6370,39 +6380,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572345</v>
+        <v>572171</v>
       </c>
       <c r="R55" t="n">
-        <v>7078154</v>
+        <v>7078312</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6434,7 +6439,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6444,12 +6449,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>78800</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R38" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,11 +4671,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>78800</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R39" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4773,6 +4768,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5130,32 +5130,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968885</v>
+        <v>128968889</v>
       </c>
       <c r="B43" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572164</v>
+        <v>572173</v>
       </c>
       <c r="R43" t="n">
-        <v>7078161</v>
+        <v>7078310</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5201,6 +5201,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5227,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>78800</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,37 +5243,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R44" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5295,14 +5300,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5317,60 +5327,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128964737</v>
+        <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>78800</v>
+        <v>98710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572174</v>
+        <v>572164</v>
       </c>
       <c r="R45" t="n">
-        <v>7078301</v>
+        <v>7078161</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5397,19 +5407,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5424,12 +5424,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,42 +3363,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R26" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,24 +3420,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3465,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R27" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,14 +3527,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
         <v>128968877</v>
       </c>
       <c r="B28" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>128968884</v>
       </c>
       <c r="B32" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>128968876</v>
       </c>
       <c r="B33" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128965337</v>
+        <v>128968889</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5054,17 +5054,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572328</v>
+        <v>572173</v>
       </c>
       <c r="R42" t="n">
-        <v>7078189</v>
+        <v>7078310</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,19 +5091,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5118,22 +5113,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5141,37 +5136,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R43" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5198,14 +5193,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B44" t="n">
-        <v>78800</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R44" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>128965015</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R48" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B49" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R49" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,45 +5834,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128964698</v>
+        <v>128966090</v>
       </c>
       <c r="B50" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572170</v>
+        <v>572227</v>
       </c>
       <c r="R50" t="n">
-        <v>7078313</v>
+        <v>7078263</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5904,7 +5909,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5914,7 +5919,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5929,62 +5939,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>92827</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R51" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6016,7 +6021,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6026,12 +6031,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6046,12 +6046,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6061,7 +6061,7 @@
         <v>128968880</v>
       </c>
       <c r="B52" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6155,53 +6155,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>92827</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R53" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6228,24 +6223,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6260,60 +6240,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128968894</v>
+        <v>128965429</v>
       </c>
       <c r="B54" t="n">
-        <v>92825</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572170</v>
+        <v>572345</v>
       </c>
       <c r="R54" t="n">
-        <v>7078122</v>
+        <v>7078154</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6340,9 +6325,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6357,12 +6357,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6372,7 +6372,7 @@
         <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,37 +3363,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R26" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3420,14 +3425,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3442,22 +3457,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,42 +3480,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R27" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3527,24 +3537,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,48 +4172,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B34" t="n">
-        <v>92827</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R34" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,9 +4245,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,65 +4277,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>92831</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R35" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4342,24 +4357,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B38" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R38" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,6 +4671,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4697,10 +4702,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4732,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R39" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4768,11 +4773,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R43" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128965337</v>
+        <v>128964737</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572328</v>
+        <v>572174</v>
       </c>
       <c r="R44" t="n">
-        <v>7078189</v>
+        <v>7078301</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B48" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R48" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R49" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5951,48 +5951,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128964698</v>
+        <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>92827</v>
+        <v>91570</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572170</v>
+        <v>572367</v>
       </c>
       <c r="R51" t="n">
-        <v>7078313</v>
+        <v>7078119</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6019,19 +6019,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6046,60 +6036,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128968880</v>
+        <v>128964698</v>
       </c>
       <c r="B52" t="n">
-        <v>91566</v>
+        <v>92831</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572367</v>
+        <v>572170</v>
       </c>
       <c r="R52" t="n">
-        <v>7078119</v>
+        <v>7078313</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6126,9 +6116,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,60 +6143,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968894</v>
+        <v>128965429</v>
       </c>
       <c r="B53" t="n">
-        <v>92827</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572170</v>
+        <v>572345</v>
       </c>
       <c r="R53" t="n">
-        <v>7078122</v>
+        <v>7078154</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,9 +6228,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,22 +6260,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128965429</v>
+        <v>128964712</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6263,39 +6283,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572345</v>
+        <v>572171</v>
       </c>
       <c r="R54" t="n">
-        <v>7078154</v>
+        <v>7078312</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6327,7 +6342,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6337,12 +6352,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,48 +6379,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6437,19 +6447,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6464,12 +6464,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3671,7 +3671,7 @@
         <v>128968881</v>
       </c>
       <c r="B29" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>128968895</v>
       </c>
       <c r="B30" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>128965861</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,53 +4172,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R34" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4245,24 +4240,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4277,60 +4257,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B35" t="n">
-        <v>92831</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R35" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4357,9 +4342,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4389,7 +4389,7 @@
         <v>128964635</v>
       </c>
       <c r="B36" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>128965451</v>
       </c>
       <c r="B37" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,10 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128968888</v>
+        <v>128968883</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4611,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>572295</v>
+        <v>572274</v>
       </c>
       <c r="R38" t="n">
-        <v>7078272</v>
+        <v>7078160</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4671,11 +4671,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,10 +4697,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128968883</v>
+        <v>128968888</v>
       </c>
       <c r="B39" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>572274</v>
+        <v>572295</v>
       </c>
       <c r="R39" t="n">
-        <v>7078160</v>
+        <v>7078272</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4773,6 +4768,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4802,7 +4802,7 @@
         <v>128964926</v>
       </c>
       <c r="B40" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5125,10 +5125,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128965337</v>
+        <v>128964737</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5136,21 +5136,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5160,10 +5160,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572328</v>
+        <v>572174</v>
       </c>
       <c r="R43" t="n">
-        <v>7078189</v>
+        <v>7078301</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,22 +5220,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128964737</v>
+        <v>128965337</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572174</v>
+        <v>572328</v>
       </c>
       <c r="R44" t="n">
-        <v>7078301</v>
+        <v>7078189</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,12 +5327,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>128968885</v>
       </c>
       <c r="B45" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>128968878</v>
       </c>
       <c r="B46" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,32 +5640,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128968890</v>
+        <v>128968886</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>572275</v>
+        <v>572202</v>
       </c>
       <c r="R48" t="n">
-        <v>7078193</v>
+        <v>7078207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5737,32 +5737,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128968886</v>
+        <v>128968890</v>
       </c>
       <c r="B49" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>572202</v>
+        <v>572275</v>
       </c>
       <c r="R49" t="n">
-        <v>7078207</v>
+        <v>7078193</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5834,50 +5834,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128966090</v>
+        <v>128964698</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>572227</v>
+        <v>572170</v>
       </c>
       <c r="R50" t="n">
-        <v>7078263</v>
+        <v>7078313</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5909,7 +5904,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5919,12 +5914,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5939,12 +5929,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5954,7 +5944,7 @@
         <v>128968880</v>
       </c>
       <c r="B51" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6048,45 +6038,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128964698</v>
+        <v>128966090</v>
       </c>
       <c r="B52" t="n">
-        <v>92831</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572170</v>
+        <v>572227</v>
       </c>
       <c r="R52" t="n">
-        <v>7078313</v>
+        <v>7078263</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6118,7 +6113,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6128,7 +6123,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,65 +6143,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128965429</v>
+        <v>128968894</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572345</v>
+        <v>572170</v>
       </c>
       <c r="R53" t="n">
-        <v>7078154</v>
+        <v>7078122</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6228,24 +6223,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6260,22 +6240,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128964712</v>
+        <v>128965429</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6283,34 +6263,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>572171</v>
+        <v>572345</v>
       </c>
       <c r="R54" t="n">
-        <v>7078312</v>
+        <v>7078154</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6342,7 +6327,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6352,7 +6337,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6379,48 +6369,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B55" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R55" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6447,9 +6437,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6464,12 +6464,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6479,7 +6479,7 @@
         <v>128968892</v>
       </c>
       <c r="B56" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 22528-2021 artfynd.xlsx
+++ b/artfynd/A 22528-2021 artfynd.xlsx
@@ -3352,10 +3352,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128965870</v>
+        <v>128968887</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3363,42 +3363,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>572300</v>
+        <v>572338</v>
       </c>
       <c r="R26" t="n">
-        <v>7078026</v>
+        <v>7078208</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3425,24 +3420,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3457,22 +3442,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128968887</v>
+        <v>128965870</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,37 +3465,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>572338</v>
+        <v>572300</v>
       </c>
       <c r="R27" t="n">
-        <v>7078208</v>
+        <v>7078026</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3537,14 +3527,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,12 +3559,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4172,48 +4172,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128968896</v>
+        <v>128965271</v>
       </c>
       <c r="B34" t="n">
-        <v>92832</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>572340</v>
+        <v>572324</v>
       </c>
       <c r="R34" t="n">
-        <v>7078177</v>
+        <v>7078221</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4240,9 +4245,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4257,65 +4277,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128965271</v>
+        <v>128968896</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>92832</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>572324</v>
+        <v>572340</v>
       </c>
       <c r="R35" t="n">
-        <v>7078221</v>
+        <v>7078177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4342,24 +4357,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4374,12 +4374,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128968889</v>
+        <v>128964737</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5034,37 +5034,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>572173</v>
+        <v>572174</v>
       </c>
       <c r="R42" t="n">
-        <v>7078310</v>
+        <v>7078301</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5091,14 +5091,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5113,60 +5118,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128964737</v>
+        <v>128968885</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>98724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>572174</v>
+        <v>572164</v>
       </c>
       <c r="R43" t="n">
-        <v>7078301</v>
+        <v>7078161</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5193,19 +5198,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5220,19 +5215,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128965337</v>
+        <v>128968889</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5263,17 +5258,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>572328</v>
+        <v>572173</v>
       </c>
       <c r="R44" t="n">
-        <v>7078189</v>
+        <v>7078310</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5300,19 +5295,14 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:50</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5327,60 +5317,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128968885</v>
+        <v>128965337</v>
       </c>
       <c r="B45" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>572164</v>
+        <v>572328</v>
       </c>
       <c r="R45" t="n">
-        <v>7078161</v>
+        <v>7078189</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5407,9 +5397,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5424,12 +5424,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5941,10 +5941,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128968880</v>
+        <v>128966090</v>
       </c>
       <c r="B51" t="n">
-        <v>91571</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5952,37 +5952,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>572367</v>
+        <v>572227</v>
       </c>
       <c r="R51" t="n">
-        <v>7078119</v>
+        <v>7078263</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6009,9 +6014,24 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6026,22 +6046,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128966090</v>
+        <v>128968880</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>91571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6049,42 +6069,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>572227</v>
+        <v>572367</v>
       </c>
       <c r="R52" t="n">
-        <v>7078263</v>
+        <v>7078119</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6111,24 +6126,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6143,60 +6143,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128968894</v>
+        <v>128964712</v>
       </c>
       <c r="B53" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>572170</v>
+        <v>572171</v>
       </c>
       <c r="R53" t="n">
-        <v>7078122</v>
+        <v>7078312</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6223,9 +6223,19 @@
           <t>2025-10-07</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6240,12 +6250,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6369,48 +6379,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128964712</v>
+        <v>128968894</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Källmyrlokarna, Källmyrlokarna, Ång</t>
+          <t>Källmyrlokarna, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>572171</v>
+        <v>572170</v>
       </c>
       <c r="R55" t="n">
-        <v>7078312</v>
+        <v>7078122</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6437,19 +6447,9 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6464,12 +6464,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
